--- a/excel/3F.xlsx
+++ b/excel/3F.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dennis Ponce\Desktop\VISOR DE PROYECTOS EXCEL\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dennis Ponce\Desktop\sistema_de_control_de_cosechas\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F26C339E-D453-4C46-9E32-7D8FAB0D1920}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBD036D8-2A27-4552-AA38-72BE4FC0B6E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="340" yWindow="260" windowWidth="18250" windowHeight="9710" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="15">
   <si>
     <t>CICLO</t>
   </si>
@@ -58,6 +58,18 @@
   </si>
   <si>
     <t>PROGRESO</t>
+  </si>
+  <si>
+    <t>NC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PV </t>
+  </si>
+  <si>
+    <t>PP</t>
   </si>
 </sst>
 </file>
@@ -487,10 +499,18 @@
       <c r="I1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
+      <c r="J1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
@@ -520,10 +540,10 @@
       <c r="I2" s="8">
         <v>1</v>
       </c>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
@@ -553,10 +573,10 @@
       <c r="I3" s="8">
         <v>1</v>
       </c>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="3"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
@@ -586,10 +606,10 @@
       <c r="I4" s="8">
         <v>1</v>
       </c>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="3"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
@@ -619,10 +639,10 @@
       <c r="I5" s="8">
         <v>1</v>
       </c>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
+      <c r="J5" s="3"/>
+      <c r="K5" s="3"/>
+      <c r="L5" s="3"/>
+      <c r="M5" s="3"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="B6" s="2"/>
